--- a/estandar-a/templates/4-4-1-reporte-evaluacion-resultados.xlsx
+++ b/estandar-a/templates/4-4-1-reporte-evaluacion-resultados.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Afacad"/>
+      <color rgb="004B5563"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Afacad"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
@@ -43,7 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00193B69"/>
+        <fgColor rgb="0028467E"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,11 +63,11 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -448,7 +454,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Reporte de evaluación de resultados Manual de Implementar IA · Producto del Elemento 3 · Evaluar · Excel</t>
+          <t>Reporte de evaluación de resultados de la adopción de soluciones de IA Curso de Adopción de IA en procesos · Producto del Elemento 3 · Evaluar · Excel</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -549,7 +555,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Indicadores · línea base · valor actual · variación Tabla con cada indicador del proyecto, su valor antes de la implementación, su valor actual, y la variación porcentual.</t>
+          <t>Indicadores · línea base · valor actual · variación Tabla con cada indicador del proyecto, su valor antes de la adopción, su valor actual, y la variación porcentual.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
